--- a/QA/reports/Load_Test_Report.xlsx
+++ b/QA/reports/Load_Test_Report.xlsx
@@ -541,7 +541,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Executed on: 2026-07-30 10:08:22 | Target VUs: 300 | Duration: 1 minute</t>
+          <t>Executed on: 2026-07-30 10:53:25 | Target VUs: 300 | Duration: 1 minute</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>47,166</t>
+          <t>36,085</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>762.84 req/s</t>
+          <t>586.50 req/s</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>0.99 ms</t>
+          <t>1.05 ms</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>370.05 ms</t>
+          <t>477.64 ms</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>2081.80 ms</t>
+          <t>2326.70 ms</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2025.61 ms</t>
+          <t>1560.50 ms</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>2036.66 ms</t>
+          <t>2034.03 ms</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>90.97%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>9.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
